--- a/resources/templates/standard/L2300-05.xlsx
+++ b/resources/templates/standard/L2300-05.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="29">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>◆ 년/2회 검교정 실시.</t>
   </si>
@@ -951,7 +954,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="35.1" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -1075,7 +1080,7 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -1092,7 +1097,7 @@
       <c r="N4" s="9"/>
       <c r="O4" s="9"/>
       <c r="P4" s="10" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
@@ -1120,10 +1125,10 @@
     </row>
     <row r="5" ht="13.5" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -1132,17 +1137,17 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
       <c r="I5" s="13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N5" s="16"/>
       <c r="O5" s="16"/>
@@ -1156,7 +1161,7 @@
       <c r="W5" s="16"/>
       <c r="X5" s="16"/>
       <c r="Y5" s="17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z5" s="17"/>
       <c r="AA5" s="5"/>
@@ -1186,43 +1191,43 @@
       <c r="J6" s="13"/>
       <c r="K6" s="14"/>
       <c r="L6" s="18" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M6" s="19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O6" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P6" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q6" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S6" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T6" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U6" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V6" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W6" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X6" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y6" s="17"/>
       <c r="Z6" s="17"/>
@@ -1255,7 +1260,7 @@
       <c r="J7" s="22"/>
       <c r="K7" s="23"/>
       <c r="L7" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
@@ -1298,7 +1303,7 @@
       <c r="J8" s="22"/>
       <c r="K8" s="23"/>
       <c r="L8" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M8" s="28"/>
       <c r="N8" s="28"/>
@@ -1343,7 +1348,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="23"/>
       <c r="L9" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
@@ -1386,7 +1391,7 @@
       <c r="J10" s="22"/>
       <c r="K10" s="23"/>
       <c r="L10" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M10" s="28"/>
       <c r="N10" s="28"/>
@@ -1431,7 +1436,7 @@
       <c r="J11" s="22"/>
       <c r="K11" s="23"/>
       <c r="L11" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
@@ -1474,7 +1479,7 @@
       <c r="J12" s="22"/>
       <c r="K12" s="23"/>
       <c r="L12" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M12" s="28"/>
       <c r="N12" s="28"/>
@@ -1519,7 +1524,7 @@
       <c r="J13" s="22"/>
       <c r="K13" s="23"/>
       <c r="L13" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M13" s="25"/>
       <c r="N13" s="25"/>
@@ -1562,7 +1567,7 @@
       <c r="J14" s="22"/>
       <c r="K14" s="23"/>
       <c r="L14" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M14" s="28"/>
       <c r="N14" s="28"/>
@@ -1607,7 +1612,7 @@
       <c r="J15" s="22"/>
       <c r="K15" s="23"/>
       <c r="L15" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M15" s="25"/>
       <c r="N15" s="25"/>
@@ -1650,7 +1655,7 @@
       <c r="J16" s="22"/>
       <c r="K16" s="23"/>
       <c r="L16" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M16" s="28"/>
       <c r="N16" s="28"/>
@@ -1695,7 +1700,7 @@
       <c r="J17" s="22"/>
       <c r="K17" s="23"/>
       <c r="L17" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M17" s="25"/>
       <c r="N17" s="25"/>
@@ -1738,7 +1743,7 @@
       <c r="J18" s="22"/>
       <c r="K18" s="23"/>
       <c r="L18" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M18" s="28"/>
       <c r="N18" s="28"/>
@@ -1783,7 +1788,7 @@
       <c r="J19" s="22"/>
       <c r="K19" s="23"/>
       <c r="L19" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M19" s="25"/>
       <c r="N19" s="25"/>
@@ -1826,7 +1831,7 @@
       <c r="J20" s="22"/>
       <c r="K20" s="23"/>
       <c r="L20" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M20" s="28"/>
       <c r="N20" s="28"/>
@@ -1871,7 +1876,7 @@
       <c r="J21" s="22"/>
       <c r="K21" s="23"/>
       <c r="L21" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M21" s="25"/>
       <c r="N21" s="25"/>
@@ -1914,7 +1919,7 @@
       <c r="J22" s="22"/>
       <c r="K22" s="23"/>
       <c r="L22" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M22" s="28"/>
       <c r="N22" s="28"/>
@@ -1959,7 +1964,7 @@
       <c r="J23" s="22"/>
       <c r="K23" s="23"/>
       <c r="L23" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M23" s="25"/>
       <c r="N23" s="25"/>
@@ -2002,7 +2007,7 @@
       <c r="J24" s="22"/>
       <c r="K24" s="23"/>
       <c r="L24" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M24" s="28"/>
       <c r="N24" s="28"/>
@@ -2047,7 +2052,7 @@
       <c r="J25" s="22"/>
       <c r="K25" s="23"/>
       <c r="L25" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M25" s="25"/>
       <c r="N25" s="25"/>
@@ -2090,7 +2095,7 @@
       <c r="J26" s="22"/>
       <c r="K26" s="23"/>
       <c r="L26" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M26" s="28"/>
       <c r="N26" s="28"/>
@@ -2135,7 +2140,7 @@
       <c r="J27" s="22"/>
       <c r="K27" s="23"/>
       <c r="L27" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M27" s="25"/>
       <c r="N27" s="25"/>
@@ -2178,7 +2183,7 @@
       <c r="J28" s="22"/>
       <c r="K28" s="23"/>
       <c r="L28" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M28" s="28"/>
       <c r="N28" s="28"/>
@@ -2223,7 +2228,7 @@
       <c r="J29" s="22"/>
       <c r="K29" s="23"/>
       <c r="L29" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
@@ -2266,7 +2271,7 @@
       <c r="J30" s="22"/>
       <c r="K30" s="23"/>
       <c r="L30" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M30" s="28"/>
       <c r="N30" s="28"/>
@@ -2311,7 +2316,7 @@
       <c r="J31" s="22"/>
       <c r="K31" s="23"/>
       <c r="L31" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
@@ -2354,7 +2359,7 @@
       <c r="J32" s="22"/>
       <c r="K32" s="23"/>
       <c r="L32" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M32" s="28"/>
       <c r="N32" s="28"/>
@@ -2399,7 +2404,7 @@
       <c r="J33" s="22"/>
       <c r="K33" s="23"/>
       <c r="L33" s="24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
@@ -2442,7 +2447,7 @@
       <c r="J34" s="22"/>
       <c r="K34" s="23"/>
       <c r="L34" s="27" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M34" s="28"/>
       <c r="N34" s="28"/>
@@ -2489,7 +2494,7 @@
       <c r="J35" s="22"/>
       <c r="K35" s="23"/>
       <c r="L35" s="30" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
@@ -2532,7 +2537,7 @@
       <c r="J36" s="22"/>
       <c r="K36" s="23"/>
       <c r="L36" s="30" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M36" s="28"/>
       <c r="N36" s="28"/>
@@ -2564,7 +2569,7 @@
     </row>
     <row r="37" ht="12" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A37" s="31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
@@ -2718,30 +2723,30 @@
       <c r="AB40" s="35"/>
       <c r="AC40" s="37"/>
       <c r="AD40" s="38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE40" s="39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF40" s="39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG40" s="39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH40" s="40"/>
       <c r="AI40" s="35"/>
       <c r="AJ40" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="AK40" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL40" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM40" s="39" t="s">
         <v>27</v>
-      </c>
-      <c r="AK40" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="AL40" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="AM40" s="39" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="41" ht="20.1" customHeight="1" spans="1:39" x14ac:dyDescent="0.25">
